--- a/tiflow-diga/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-EX-DeepLink.xlsx
+++ b/tiflow-diga/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-EX-DeepLink.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1324,7 +1324,7 @@
         <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>108</v>
